--- a/Config/Excels/Tables/U-UIConfig-UI配置表.xlsx
+++ b/Config/Excels/Tables/U-UIConfig-UI配置表.xlsx
@@ -183,10 +183,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -209,9 +209,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,13 +239,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -242,59 +286,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,6 +299,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -316,16 +330,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -337,23 +352,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,55 +368,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,13 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,109 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,17 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -596,7 +584,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -617,6 +605,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -632,16 +635,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -665,173 +668,175 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1154,400 +1159,401 @@
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="8" width="17" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1"/>
+    <col min="2" max="2" width="25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15" style="2" customWidth="1"/>
+    <col min="4" max="8" width="17" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>0.3</v>
       </c>
-      <c r="G5" s="2" t="b">
+      <c r="G5" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="b">
+      <c r="H5" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>0.3</v>
       </c>
-      <c r="G6" s="2" t="b">
+      <c r="G6" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="b">
+      <c r="H6" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>0.3</v>
       </c>
-      <c r="G7" s="2" t="b">
+      <c r="G7" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H7" s="2" t="b">
+      <c r="H7" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>0.3</v>
       </c>
-      <c r="G8" s="2" t="b">
+      <c r="G8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="b">
+      <c r="H8" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>0.3</v>
       </c>
-      <c r="G9" s="2" t="b">
+      <c r="G9" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="b">
+      <c r="H9" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>0.3</v>
       </c>
-      <c r="G10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2" t="b">
+      <c r="G10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="4">
         <v>0.3</v>
       </c>
-      <c r="G11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2" t="b">
+      <c r="G11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="4">
         <v>0.3</v>
       </c>
-      <c r="G12" s="2" t="b">
+      <c r="G12" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H12" s="2" t="b">
+      <c r="H12" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="4">
         <v>0.3</v>
       </c>
-      <c r="G13" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="b">
+      <c r="G13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="4">
         <v>0.3</v>
       </c>
-      <c r="G14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="b">
+      <c r="G14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="4">
         <v>0.3</v>
       </c>
-      <c r="G15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="b">
+      <c r="G15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="4">
         <v>0.3</v>
       </c>
-      <c r="G16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2" t="b">
+      <c r="G16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Config/Excels/Tables/U-UIConfig-UI配置表.xlsx
+++ b/Config/Excels/Tables/U-UIConfig-UI配置表.xlsx
@@ -19,7 +19,7 @@
     <t>##var</t>
   </si>
   <si>
-    <t>UIName</t>
+    <t>Name</t>
   </si>
   <si>
     <t>##comment</t>
@@ -183,10 +183,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -210,21 +210,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -246,7 +240,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -283,9 +284,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,6 +307,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
@@ -308,7 +332,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,38 +340,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,181 +368,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,24 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -604,17 +586,29 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,6 +624,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,15 +668,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -676,10 +676,10 @@
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -688,16 +688,16 @@
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -706,115 +706,115 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Config/Excels/Tables/U-UIConfig-UI配置表.xlsx
+++ b/Config/Excels/Tables/U-UIConfig-UI配置表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56">
   <si>
     <t>##var</t>
   </si>
@@ -40,6 +40,9 @@
     <t>PauseCoveredUI</t>
   </si>
   <si>
+    <t>Blur</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -82,10 +85,17 @@
     <t>动画时长（秒）</t>
   </si>
   <si>
-    <t>是否适配刘海</t>
-  </si>
-  <si>
-    <t>被遮挡时是否暂停</t>
+    <t>是否适配刘海:
+全屏界面一般为true
+弹窗一般为false</t>
+  </si>
+  <si>
+    <t>被覆盖时是否暂停</t>
+  </si>
+  <si>
+    <t>是否模糊:
+全屏界面一般为false
+弹窗一般为true</t>
   </si>
   <si>
     <t>WinMain</t>
@@ -210,15 +220,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,7 +256,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,6 +264,37 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,76 +325,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,181 +378,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,21 +581,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -600,6 +595,51 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,36 +668,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -676,10 +686,10 @@
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -688,133 +698,133 @@
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1156,16 +1166,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="12" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12" style="1"/>
     <col min="2" max="2" width="25" style="2" customWidth="1"/>
     <col min="3" max="3" width="15" style="2" customWidth="1"/>
-    <col min="4" max="8" width="17" style="1" customWidth="1"/>
+    <col min="4" max="6" width="17" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5555555555556" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1190,98 +1203,110 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" ht="40.5" spans="1:9">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="4"/>
       <c r="B5" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F5" s="4">
         <v>0.3</v>
@@ -1292,20 +1317,23 @@
       <c r="H5" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="I5" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="F6" s="4">
         <v>0.3</v>
@@ -1316,20 +1344,23 @@
       <c r="H6" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="I6" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" s="4"/>
       <c r="B7" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7" s="4">
         <v>0.3</v>
@@ -1340,20 +1371,23 @@
       <c r="H7" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="I7" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F8" s="4">
         <v>0.3</v>
@@ -1364,20 +1398,23 @@
       <c r="H8" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="I8" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F9" s="4">
         <v>0.3</v>
@@ -1388,20 +1425,23 @@
       <c r="H9" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="I9" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F10" s="4">
         <v>0.3</v>
@@ -1412,20 +1452,23 @@
       <c r="H10" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="I10" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F11" s="4">
         <v>0.3</v>
@@ -1436,20 +1479,23 @@
       <c r="H11" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="I11" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" s="4"/>
       <c r="B12" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F12" s="4">
         <v>0.3</v>
@@ -1460,20 +1506,23 @@
       <c r="H12" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="I12" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" s="4"/>
       <c r="B13" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F13" s="4">
         <v>0.3</v>
@@ -1484,20 +1533,23 @@
       <c r="H13" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="I13" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14" s="4"/>
       <c r="B14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F14" s="4">
         <v>0.3</v>
@@ -1508,20 +1560,23 @@
       <c r="H14" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="I14" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9">
       <c r="A15" s="4"/>
       <c r="B15" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F15" s="4">
         <v>0.3</v>
@@ -1532,20 +1587,23 @@
       <c r="H15" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="I15" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" s="4"/>
       <c r="B16" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F16" s="4">
         <v>0.3</v>
@@ -1554,6 +1612,9 @@
         <v>0</v>
       </c>
       <c r="H16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Config/Excels/Tables/U-UIConfig-UI配置表.xlsx
+++ b/Config/Excels/Tables/U-UIConfig-UI配置表.xlsx
@@ -193,10 +193,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -220,6 +220,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -227,14 +250,68 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,84 +333,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -378,181 +378,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,11 +581,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,21 +644,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -653,21 +668,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -686,10 +686,10 @@
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -698,7 +698,7 @@
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -707,10 +707,10 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -719,112 +719,112 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1501,13 +1501,13 @@
         <v>0.3</v>
       </c>
       <c r="G12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="b">
         <v>1</v>
-      </c>
-      <c r="H12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9">
